--- a/output/pdf_financials_xlsx/SPC.xlsx
+++ b/output/pdf_financials_xlsx/SPC.xlsx
@@ -799,22 +799,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.932427</v>
+        <v>-0.932427</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>4.310163</v>
+        <v>-4.310163</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4.50496</v>
+        <v>-4.50496</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>4.354018</v>
+        <v>-4.354018</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.191165</v>
+        <v>-2.191165</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3.022907</v>
+        <v>-3.022907</v>
       </c>
     </row>
     <row r="17">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.932427</v>
+        <v>-0.932427</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4.310163</v>
+        <v>-4.310163</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>4.50496</v>
+        <v>-4.50496</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4.354018</v>
+        <v>-4.354018</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.191165</v>
+        <v>-2.191165</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3.022907</v>
+        <v>-3.022907</v>
       </c>
     </row>
     <row r="21">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.932427</v>
+        <v>-0.932427</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>4.310163</v>
+        <v>-4.310163</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>4.50496</v>
+        <v>-4.50496</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>4.354018</v>
+        <v>-4.354018</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.191165</v>
+        <v>-2.191165</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3.022907</v>
+        <v>-3.022907</v>
       </c>
     </row>
     <row r="24">
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-46.62135</v>
+        <v>46.62135</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-86.20326</v>
+        <v>86.20326</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-112.624</v>
+        <v>112.624</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-145.133933</v>
+        <v>145.133933</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.932427</v>
+        <v>-0.932427</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4.310163</v>
+        <v>-4.310163</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4.50496</v>
+        <v>-4.50496</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4.354018</v>
+        <v>-4.354018</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.191165</v>
+        <v>-2.191165</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>3.022907</v>
+        <v>-3.022907</v>
       </c>
     </row>
     <row r="28">
@@ -1152,22 +1152,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.932427</v>
+        <v>-0.932427</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>4.331279</v>
+        <v>-4.289047</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.536981</v>
+        <v>-4.472939</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4.386931</v>
+        <v>-4.321105</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.233218</v>
+        <v>-2.149112</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3.061499</v>
+        <v>-2.984315</v>
       </c>
     </row>
     <row r="30">
@@ -1214,22 +1214,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2757,22 +2757,22 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.196586</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.634344</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.039793</v>
+        <v>1.961926</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>1.256793</v>
+        <v>2.125594</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>1.3662</v>
+        <v>1.650064</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>1.11864</v>
+        <v>1.633965</v>
       </c>
     </row>
     <row r="93">
@@ -4606,7 +4606,11 @@
           <t>Warrants reserve 8</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
         <v>0.196586</v>
       </c>
@@ -7516,22 +7520,22 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0.932427</v>
+        <v>-0.932427</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>4.310163</v>
+        <v>-4.310163</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>4.50496</v>
+        <v>-4.50496</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>4.354018</v>
+        <v>-4.354018</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>2.191165</v>
+        <v>-2.191165</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>3.022907</v>
+        <v>-3.022907</v>
       </c>
     </row>
     <row r="87">

--- a/output/pdf_financials_xlsx/SPC.xlsx
+++ b/output/pdf_financials_xlsx/SPC.xlsx
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.07009799999999999</v>
+        <v>1.128953</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.529846</v>
+        <v>4.631632</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.514567</v>
+        <v>4.508082</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.605914</v>
+        <v>4.462258</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.40176</v>
+        <v>2.457075</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.5356649999999999</v>
+        <v>3.258851</v>
       </c>
     </row>
     <row r="11">
@@ -674,22 +674,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.07009799999999999</v>
+        <v>-1.128953</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.529846</v>
+        <v>-4.631632</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.514567</v>
+        <v>-4.508082</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.605914</v>
+        <v>-4.462258</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.40176</v>
+        <v>-2.457075</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.5356649999999999</v>
+        <v>-3.258851</v>
       </c>
     </row>
     <row r="12">
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003122</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.030934</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.090267</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1108,13 +1108,13 @@
         <v>-4.310163</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.50496</v>
+        <v>-4.501838</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.354018</v>
+        <v>-4.323084</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.191165</v>
+        <v>-2.100898</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-3.022907</v>
@@ -1158,13 +1158,13 @@
         <v>-4.289047</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.472939</v>
+        <v>-4.469817</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.321105</v>
+        <v>-4.290171</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.149112</v>
+        <v>-2.058845</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-2.984315</v>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">

--- a/output/pdf_financials_xlsx/SPC.xlsx
+++ b/output/pdf_financials_xlsx/SPC.xlsx
@@ -2195,22 +2195,22 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.024053</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.024053</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.027465</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.03128</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.035449</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.019548</v>
       </c>
     </row>
     <row r="71">
@@ -2220,22 +2220,22 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.024053</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.024053</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.027465</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.03128</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.035449</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.019548</v>
       </c>
     </row>
     <row r="72">
@@ -2323,19 +2323,19 @@
         <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.024053</v>
+        <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.027465</v>
+        <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.209877</v>
+        <v>0.178597</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.155603</v>
+        <v>0.120154</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.019548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2444,35 +2444,23 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.01429131636017944</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.005027005551170101</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.007216567441601376</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.01674481448747645</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.0194475425457853</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.008920280130016688</v>
       </c>
     </row>
     <row r="81">
@@ -3217,13 +3205,13 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.105896</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002418</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -3804,13 +3792,13 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.105896</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002418</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -3829,13 +3817,13 @@
         <v>-1.113185</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-3.427015</v>
+        <v>-3.532911</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-4.466403</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-3.901506</v>
+        <v>-3.903924</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-1.966029</v>
@@ -4408,7 +4396,11 @@
           <t>Current portion of lease obligation 7</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -5208,7 +5200,11 @@
           <t>Current portion of lease obligation</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>0.024053</v>
       </c>
@@ -6324,7 +6320,11 @@
           <t>Purchase of equipment 5</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -6762,7 +6762,11 @@
           <t>Purchase of equipment 6</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
